--- a/classifier/data/combined_equations.xlsx
+++ b/classifier/data/combined_equations.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0bae0c2e0fb1446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e822d02b4c84149"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38410,164 +38410,945 @@
       </x:c>
     </x:row>
     <x:row r="649">
-      <x:c r="A649"/>
-      <x:c r="B649"/>
+      <x:c r="A649" t="str">
+        <x:v>y^{\prime}=- \frac{2 \operatorname{acos}{\left(2 x \right)} \left. \frac{d}{d \xi_{1}} \operatorname{ctan}{\left(\xi_{1} \right)} \right|_{\substack{ \xi_{1}=2 x }}}{\operatorname{ctan}^{2}{\left(2 x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{ctan}{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B649" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C649"/>
       <x:c r="D649"/>
-      <x:c r="E649"/>
-      <x:c r="F649"/>
-      <x:c r="G649"/>
+      <x:c r="E649" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F649" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G649" t="str">
+        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\ctg(2 \cdot x)}-\ctg(x) \cdot \arccos(2 \cdot x)+C</x:v>
+      </x:c>
       <x:c r="H649"/>
-      <x:c r="I649"/>
-      <x:c r="J649"/>
-      <x:c r="K649"/>
-      <x:c r="L649"/>
-      <x:c r="M649"/>
-      <x:c r="N649"/>
+      <x:c r="I649" t="str">
+        <x:v>[REASONING]
+**Step 1 – Rewrite the given equation**
+\[
+y'=- \frac{2\,\operatorname{acos}(2x)\,
+\left.\dfrac{d}{d\xi_{1}}\operatorname{ctan}(\xi_{1})\right|_{\xi_{1}=2x}}
+{\operatorname{ctan}^{2}(2x)}
+-\frac{2}{\sqrt{1-4x^{2}}\;\operatorname{ctan}(2x)} .
+\]
+Here  
+* \(\operatorname{acos}\) denotes \(\arccos\),  
+* \(\operatorname{ctan}\) denotes \(\cot\), and  
+* \(\displaystyle\frac{d}{d\xi}\cot(\xi)=-\csc^{2}(\xi)\).
+Hence  
+\[
+\left.\frac{d}{d\xi_{1}}\operatorname{ctan}(\xi_{1})\right|_{\xi_{1}=2x}
+= -\csc^{2}(2x).
+\]
+**Step 2 – Substitute the derivative**
+\[
+\begin{aligned}
+y'&amp;=-\frac{2\,\operatorname{acos}(2x)\,[-\csc^{2}(2x)]}{\cot^{2}(2x)}
+-\frac{2}{\sqrt{1-4x^{2}}\;\cot(2x)}\\[4pt]
+&amp;= \frac{2\,\operatorname{acos}(2x)\,\csc^{2}(2x)}{\cot^{2}(2x)}
+-\frac{2}{\sqrt{1-4x^{2}}\;\cot(2x)} .
+\end{aligned}
+\]
+**Step 3 – Simplify the trigonometric ratio**
+Using \(\cot\theta=\dfrac{\cos\theta}{\sin\theta}\) and \(\csc\theta=\dfrac{1}{\sin\theta}\),
+\[
+\frac{\csc^{2}(2x)}{\cot^{2}(2x)}
+=\frac{1/\sin^{2}(2x)}{\cos^{2}(2x)/\sin^{2}(2x)}
+=\frac{1}{\cos^{2}(2x)}=\sec^{2}(2x).
+\]
+Also \(\displaystyle\frac{1}{\cot(2x)}=\tan(2x)\).
+Thus
+\[
+y' = 2\,\operatorname{acos}(2x)\,\sec^{2}(2x)
+      -\frac{2\,\tan(2x)}{\sqrt{1-4x^{2}}}.
+\]
+**Step 4 – Recognise a product derivative**
+Recall  
+\[
+\frac{d}{dx}\bigl[\operatorname{acos}(2x)\bigr]=-\frac{2}{\sqrt{1-4x^{2}}},\qquad
+\frac{d}{dx}\bigl[\tan(2x)\bigr]=2\sec^{2}(2x).
+\]
+Hence, by the product rule,
+\[
+\frac{d}{dx}\bigl[\operatorname{acos}(2x)\,\tan(2x)\bigr]
+= \bigl[-\frac{2}{\sqrt{1-4x^{2}}}\bigr]\tan(2x)
+  +
+[FINAL ANSWER]
+\boxed{NOT_FOUND}</x:v>
+      </x:c>
+      <x:c r="J649" t="str">
+        <x:v>y^{\prime}=-\frac{2\operatorname{acos}{(2x)}.\frac{d}{d\xi_{1}}\operatorname{ctan}{(\xi_{1})}|_{\substack{\xi_{1}=2x}}}{\operatorname{ctan}^{2}{(2x)}}-\frac{2}{\sqrt{1-4x^{2}}\operatorname{ctan}{(2x)}}</x:v>
+      </x:c>
+      <x:c r="K649" t="str">
+        <x:v>y ^ { prime } = - frac { 2 operatorname { acos } { ( 2 x ) } frac { d } { d xi _ { 1 } } operatorname { ctan } { ( xi _ { 1 } ) } _ { substack { xi _ { 1 } = 2 x } } } { operatorname { ctan } ^ { 2 } { ( 2 x ) } } - frac { 2 } { sqrt { 1 - 4 x ^ { 2 } } operatorname { ctan } { ( 2 x ) } }</x:v>
+      </x:c>
+      <x:c r="L649" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="M649" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N649" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="650">
-      <x:c r="A650"/>
-      <x:c r="B650"/>
+      <x:c r="A650" t="str">
+        <x:v>y^{\prime}=\frac{2 \cos{\left(2 x \right)}}{\operatorname{asin}{\left(2 x \right)}} - \frac{2 \sin{\left(2 x \right)}}{\sqrt{1 - 4 x^{2}} \operatorname{asin}^{2}{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B650" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C650"/>
       <x:c r="D650"/>
-      <x:c r="E650"/>
-      <x:c r="F650"/>
-      <x:c r="G650"/>
+      <x:c r="E650" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F650" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G650" t="str">
+        <x:v>y=\sin(2 \cdot x) \cdot \frac{1}{\arcsin(2 \cdot x)}-\tg(x) \cdot \ctg(x)+C</x:v>
+      </x:c>
       <x:c r="H650"/>
-      <x:c r="I650"/>
-      <x:c r="J650"/>
-      <x:c r="K650"/>
-      <x:c r="L650"/>
-      <x:c r="M650"/>
-      <x:c r="N650"/>
+      <x:c r="I650" t="str">
+        <x:v>[REASONING]
+**Solution**
+\[
+y'=\frac{2\cos (2x)}{\arcsin (2x)}-\frac{2\sin (2x)}{\sqrt{1-4x^{2}}\;(\arcsin (2x))^{2}}
+\]
+The right–hand side suggests the derivative of a quotient that contains \(\sin(2x)\) in the numerator and \(\arcsin(2x)\) in the denominator.  
+Consider  
+\[
+F(x)=\frac{2\sin (2x)}{\arcsin (2x)} .
+\]
+---
+### 1. Differentiate \(F(x)\)
+Let  
+\[
+u(x)=2\sin (2x),\qquad v(x)=\arcsin (2x).
+\]
+Then  
+\[
+u'(x)=2\cdot 2\cos (2x)=4\cos (2x),\qquad 
+v'(x)=\frac{2}{\sqrt{1-(2x)^{2}}}= \frac{2}{\sqrt{1-4x^{2}}}.
+\]
+Using the quotient rule,
+\[
+\begin{aligned}
+F'(x)&amp;=\frac{u'v-u v'}{v^{2}}\\[2mm]
+&amp;=\frac{4\cos (2x)\,\arcsin (2x)-2\sin (2x)\,\dfrac{2}{\sqrt{1-4x^{2}}}}
+      {(\arcsin (2x))^{2}}\\[2mm]
+&amp;= \frac{4\cos (2x)}{\arcsin (2x)}-
+    \frac{4\sin (2x)}{\sqrt{1-4x^{2}}\;(\arcsin (2x))^{2}} .
+\end{aligned}
+\]
+---
+### 2. Relate \(F'(x)\) to the given right‑hand side
+The given expression is exactly one‑half of \(F'(x)\):
+\[
+\frac{2\cos (2x)}{\arcsin (2x)}-
+\frac{2\sin (2x)}{\sqrt{1-4x^{2}}\;(\arcsin (2x))^{2}}
+=\frac12\,F'(x).
+\]
+Hence  
+\[
+y'=\frac12\,F'(x).
+\]
+---
+### 3. Integrate
+\[
+y=\int y'\,dx=\frac12\int F'(x)\,dx
+      =\frac12\,F(x)+C
+      =\frac12\left(\frac{2\sin (2x)}{\arcsin (2x)}\right)+C
+      =\frac{\sin (2x)}{\arcsin (2x)}+C .
+\]
+---
+\[
+\boxed{\,y=\dfrac{\sin (2x)}{\arcsin (2x)}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y=\dfrac{\sin (2x)}</x:v>
+      </x:c>
+      <x:c r="J650" t="str">
+        <x:v>y^{\prime}=\frac{2\cos{(2x)}}{\operatorname{asin}{(2x)}}-\frac{2\sin{(2x)}}{\sqrt{1-4x^{2}}\operatorname{asin}^{2}{(2x)}}</x:v>
+      </x:c>
+      <x:c r="K650" t="str">
+        <x:v>y ^ { prime } = frac { 2 cos { ( 2 x ) } } { operatorname { asin } { ( 2 x ) } } - frac { 2 sin { ( 2 x ) } } { sqrt { 1 - 4 x ^ { 2 } } operatorname { asin } ^ { 2 } { ( 2 x ) } }</x:v>
+      </x:c>
+      <x:c r="L650" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="M650" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N650" t="str">
+        <x:v>valid</x:v>
+      </x:c>
     </x:row>
     <x:row r="651">
-      <x:c r="A651"/>
-      <x:c r="B651"/>
+      <x:c r="A651" t="str">
+        <x:v>y^{\prime}=- \frac{1}{\sqrt{1 - x^{2}} \log{\left(x \right)}} - \frac{\operatorname{acos}{\left(x \right)}}{x \log{\left(x \right)}^{2}}</x:v>
+      </x:c>
+      <x:c r="B651" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C651"/>
       <x:c r="D651"/>
-      <x:c r="E651"/>
-      <x:c r="F651"/>
-      <x:c r="G651"/>
+      <x:c r="E651" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F651" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G651" t="str">
+        <x:v>y=\arccos(x) \cdot \frac{1}{\ln(x)}+\sin(2 \cdot x) \cdot x+C</x:v>
+      </x:c>
       <x:c r="H651"/>
-      <x:c r="I651"/>
-      <x:c r="J651"/>
-      <x:c r="K651"/>
-      <x:c r="L651"/>
-      <x:c r="M651"/>
-      <x:c r="N651"/>
+      <x:c r="I651" t="str">
+        <x:v>[REASONING]
+**Reasoning**
+The differential equation is  
+\[
+y'=- \frac{1}{\sqrt{1 - x^{2}}\,\log x}-\frac{\arccos x}{x\,(\log x)^{2}} .
+\]
+We look for a function whose derivative gives the right‑hand side.  
+Consider  
+\[
+f(x)=\frac{\arccos x}{\log x}.
+\]
+Compute its derivative using the product rule (or quotient rule).
+\[
+\begin{aligned}
+f'(x) &amp;= \frac{d}{dx}\Bigl[\arccos x\cdot (\log x)^{-1}\Bigr]  \\
+&amp;= (\arccos x)'\,(\log x)^{-1}
+   +\arccos x\,\frac{d}{dx}\bigl[(\log x)^{-1}\bigr].
+\end{aligned}
+\]
+1. Derivative of \(\arccos x\):
+\[
+(\arccos x)' = -\frac{1}{\sqrt{1-x^{2}}}.
+\]
+Thus the first term is  
+\[
+-\frac{1}{\sqrt{1-x^{2}}}\,\frac{1}{\log x}
+   = -\frac{1}{\sqrt{1-x^{2}}\,\log x}.
+\]
+2. Derivative of \((\log x)^{-1}\):
+\[
+\frac{d}{dx}\bigl[(\log x)^{-1}\bigr]
+   = -(\log x)^{-2}\,\frac{1}{x}
+   = -\frac{1}{x(\log x)^{2}}.
+\]
+Hence the second term is  
+\[
+\arccos x\left(-\frac{1}{x(\log x)^{2}}\right)
+   = -\frac{\arccos x}{x(\log x)^{2}}.
+\]
+Adding the two terms gives  
+\[
+f'(x)= -\frac{1}{\sqrt{1-x^{2}}\,\log x}
+        -\frac{\arccos x}{x(\log x)^{2}},
+\]
+which is exactly the right‑hand side of the differential equation. Therefore  
+\[
+y' = f'(x) \quad\Longrightarrow\quad y = f(x) + C.
+\]
+Thus the general solution is  
+\[
+y = \frac{\arccos x}{\log x} + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+**Final Answer**
+\[
+\boxed{\,y = \frac{\arccos(x)}{\log x} + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \frac{\arccos(x)}</x:v>
+      </x:c>
+      <x:c r="J651" t="str">
+        <x:v>y^{\prime}=-\frac{1}{\sqrt{1-x^{2}}\log{(x)}}-\frac{\operatorname{acos}{(x)}}{x\log{(x)}^{2}}</x:v>
+      </x:c>
+      <x:c r="K651" t="str">
+        <x:v>y ^ { prime } = - frac { 1 } { sqrt { 1 - x ^ { 2 } } log { ( x ) } } - frac { operatorname { acos } { ( x ) } } { x log { ( x ) } ^ { 2 } }</x:v>
+      </x:c>
+      <x:c r="L651" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="M651" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N651" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="652">
-      <x:c r="A652"/>
-      <x:c r="B652"/>
+      <x:c r="A652" t="str">
+        <x:v>y^{\prime}=\frac{2}{\left(4 x^{2} + 1\right) \operatorname{asin}{\left(x \right)}} - \frac{\operatorname{atan}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B652" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C652"/>
       <x:c r="D652"/>
-      <x:c r="E652"/>
-      <x:c r="F652"/>
-      <x:c r="G652"/>
+      <x:c r="E652" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F652" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G652" t="str">
+        <x:v>y=\arctg(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+\ctg(2 \cdot x) \cdot \sin(2 \cdot x)+C</x:v>
+      </x:c>
       <x:c r="H652"/>
-      <x:c r="I652"/>
-      <x:c r="J652"/>
-      <x:c r="K652"/>
-      <x:c r="L652"/>
-      <x:c r="M652"/>
-      <x:c r="N652"/>
+      <x:c r="I652" t="str">
+        <x:v>[REASONING]
+**Step‑by‑step solution**
+\[
+y'=\frac{2}{\bigl(4x^{2}+1\bigr)\,\arcsin x}
+      -\frac{\arctan (2x)}{\sqrt{1-x^{2}}\;\bigl(\arcsin x\bigr)^{2}}
+\]
+---
+### 1.  Look for a function whose derivative gives the right‑hand side  
+Consider the quotient  
+\[
+u(x)=\frac{\arctan (2x)}{\arcsin x}.
+\]
+Its derivative, using the quotient rule \(\displaystyle \frac{d}{dx}\frac{u}{v}= \frac{u'v-u v'}{v^{2}}\), is  
+\[
+\begin{aligned}
+u'(x) &amp;=\frac{ \displaystyle\frac{d}{dx}\bigl[\arctan (2x)\bigr]\;\arcsin x
+        -\arctan (2x)\;\displaystyle\frac{d}{dx}\bigl[\arcsin x\bigr]}
+        {\bigl(\arcsin x\bigr)^{2}} .
+\end{aligned}
+\]
+Compute the two derivatives:
+* \(\displaystyle \frac{d}{dx}\bigl[\arctan (2x)\bigr]=\frac{2}{1+(2x)^{2}}
+        =\frac{2}{4x^{2}+1}\).
+* \(\displaystyle \frac{d}{dx}\bigl[\arcsin x\bigr]=\frac{1}{\sqrt{1-x^{2}}}\).
+Insert them:
+\[
+\begin{aligned}
+u'(x) &amp;=
+\frac{ \displaystyle \frac{2}{4x^{2}+1}\,\arcsin x
+        -\arctan (2x)\,\frac{1}{\sqrt{1-x^{2}}}}
+        {\bigl(\arcsin x\bigr)^{2}} \\[4pt]
+&amp;= \frac{2}{(4x^{2}+1)\,\arcsin x}
+   -\frac{\arctan (2x)}{\sqrt{1-x^{2}}\;(\arcsin x)^{2}} .
+\end{aligned}
+\]
+The obtained expression is exactly the right‑hand side of the given differential
+equation. Hence  
+\[
+y' = \frac{d}{dx}\!\left(\frac{\arctan (2x)}{\arcsin x}\right).
+\]
+---
+### 2.  Integrate  
+\[
+\int y'\,dx = \int \frac{d}{dx}\!\left(\frac{\arctan (2x)}{\arcsin x}\right)dx
+\quad\Longrightarrow\quad
+y = \frac{\arctan (2x)}{\arcsin x}+C,
+\]
+where \(C\) is an arbitrary constant of integration.
+---
+\[
+\boxed{\,y(x)=\frac{\displaystyle\arctan(2x)}{\displaystyle\arcsin(x)}+C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\displaystyle\arctan(2x)}</x:v>
+      </x:c>
+      <x:c r="J652" t="str">
+        <x:v>y^{\prime}=\frac{2}{(4x^{2}+1)\operatorname{asin}{(x)}}-\frac{\operatorname{atan}{(2x)}}{\sqrt{1-x^{2}}\operatorname{asin}^{2}{(x)}}</x:v>
+      </x:c>
+      <x:c r="K652" t="str">
+        <x:v>y ^ { prime } = frac { 2 } { ( 4 x ^ { 2 } + 1 ) operatorname { asin } { ( x ) } } - frac { operatorname { atan } { ( 2 x ) } } { sqrt { 1 - x ^ { 2 } } operatorname { asin } ^ { 2 } { ( x ) } }</x:v>
+      </x:c>
+      <x:c r="L652" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="M652" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N652" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="653">
-      <x:c r="A653"/>
-      <x:c r="B653"/>
+      <x:c r="A653" t="str">
+        <x:v>y^{\prime}=- e^{- x} \operatorname{ctan}{\left(x \right)} \log{\left(e \right)} + e^{- x} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}</x:v>
+      </x:c>
+      <x:c r="B653" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C653"/>
       <x:c r="D653"/>
-      <x:c r="E653"/>
-      <x:c r="F653"/>
-      <x:c r="G653"/>
+      <x:c r="E653" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F653" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G653" t="str">
+        <x:v>y=\ctg(x) \cdot \frac{1}{e^{x}}-\arcsin(2 \cdot x) \cdot \tg(2 \cdot x)+C</x:v>
+      </x:c>
       <x:c r="H653"/>
-      <x:c r="I653"/>
-      <x:c r="J653"/>
-      <x:c r="K653"/>
-      <x:c r="L653"/>
-      <x:c r="M653"/>
-      <x:c r="N653"/>
+      <x:c r="I653" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The given differential equation is  
+\[
+y'=- e^{- x}\,\operatorname{ctan}(x)\,\log(e)+e^{- x}\,\frac{d}{dx}\operatorname{ctan}(x).
+\]
+1. **Simplify constants and notation**  
+   \[
+   \log(e)=1,\qquad \operatorname{ctan}(x)=\cot x .
+   \]
+   Hence  
+   \[
+   y'=- e^{-x}\cot x+e^{-x}\frac{d}{dx}\cot x .
+   \]
+2. **Differentiate \(\cot x\)**  
+   \[
+   \frac{d}{dx}\cot x = -\csc^{2}x .
+   \]
+   Substituting,  
+   \[
+   y'=- e^{-x}\cot x+e^{-x}\bigl(-\csc^{2}x\bigr)
+      =-e^{-x}\bigl(\cot x+\csc^{2}x\bigr).
+   \]
+3. **Recognise a total derivative**  
+   Compute the derivative of the product \(e^{-x}\cot x\):
+   \[
+   \frac{d}{dx}\bigl(e^{-x}\cot x\bigr)
+   =(-e^{-x})\cot x+e^{-x}\frac{d}{dx}\cot x
+   =-e^{-x}\cot x+e^{-x}\bigl(-\csc^{2}x\bigr)
+   =-e^{-x}\bigl(\cot x+\csc^{2}x\bigr).
+   \]
+   This is exactly the right‑hand side of the differential equation, i.e.
+   \[
+   y'=\frac{d}{dx}\bigl(e^{-x}\cot x\bigr).
+   \]
+4. **Integrate**  
+   Since the derivative of \(e^{-x}\cot x\) equals \(y'\),
+   \[
+   y = e^{-x}\cot x + C,
+   \]
+   where \(C\) is an arbitrary constant of integration.
+[FINAL ANSWER]
+\[
+\boxed{\,y(x)=e^{-x}\cot x + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y(x)=e^{-x}</x:v>
+      </x:c>
+      <x:c r="J653" t="str">
+        <x:v>y^{\prime}=-exp(-x)\operatorname{ctan}{(x)}\log{(e)}+exp(-x)(d)/(dx)\operatorname{ctan}{(x)}</x:v>
+      </x:c>
+      <x:c r="K653" t="str">
+        <x:v>y ^ { prime } = - exp ( - x ) operatorname { ctan } { ( x ) } log { ( e ) } + exp ( - x ) ( d ) / ( dx ) operatorname { ctan } { ( x ) }</x:v>
+      </x:c>
+      <x:c r="L653" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="M653" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N653" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="654">
-      <x:c r="A654"/>
-      <x:c r="B654"/>
+      <x:c r="A654" t="str">
+        <x:v>y^{\prime}=- \frac{\operatorname{acot}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}} - \frac{1}{\left(x^{2} + 1\right) \operatorname{ctan}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B654" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C654"/>
       <x:c r="D654"/>
-      <x:c r="E654"/>
-      <x:c r="F654"/>
-      <x:c r="G654"/>
+      <x:c r="E654" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F654" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G654" t="str">
+        <x:v>y=\arcctg(x) \cdot \frac{1}{\ctg(x)}+\arccos(2 \cdot x) \cdot \tg(x)+C</x:v>
+      </x:c>
       <x:c r="H654"/>
-      <x:c r="I654"/>
-      <x:c r="J654"/>
-      <x:c r="K654"/>
-      <x:c r="L654"/>
-      <x:c r="M654"/>
-      <x:c r="N654"/>
+      <x:c r="I654" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The differential equation is  
+\[
+y'=- \frac{\operatorname{acot}{\left(x \right)} \frac{d}{d x} \operatorname{ctan}{\left(x \right)}}{\operatorname{ctan}^{2}{\left(x \right)}}-\frac{1}{\left(x^{2}+1\right)\operatorname{ctan}{\left(x \right)}} .
+\]
+Here \(\operatorname{ctan}(x)=\cot x\) and \(\operatorname{acot}(x)=\arccot x\).
+---
+### 1.  Compute \(\dfrac{d}{dx}\cot x\)
+\[
+\frac{d}{dx}\cot x = -\csc^{2}x = -(1+\cot^{2}x).
+\]
+---
+### 2.  Substitute the derivative
+\[
+\begin{aligned}
+y' &amp;=
+-\,\frac{\arccot x\;(-\csc^{2}x)}{\cot^{2}x}
+-\frac{1}{(x^{2}+1)\cot x}\\[4pt]
+&amp;= \frac{\arccot x\,\csc^{2}x}{\cot^{2}x}
+-\frac{1}{(x^{2}+1)\cot x}.
+\end{aligned}
+\]
+Because \(\csc^{2}x = 1+\cot^{2}x\),
+\[
+\frac{\csc^{2}x}{\cot^{2}x}= \frac{1+\cot^{2}x}{\cot^{2}x}= \frac{1}{\cot^{2}x}+1
+= \tan^{2}x+1 = \sec^{2}x .
+\]
+Hence  
+\[
+y' = \arccot x\,\sec^{2}x-\frac{1}{(x^{2}+1)\cot x}.
+\]
+---
+### 3.  Recognise a total derivative  
+Recall  
+\[
+\frac{d}{dx}\tan x = \sec^{2}x ,\qquad 
+\frac{d}{dx}\arccot x = -\frac{1}{1+x^{2}} .
+\]
+Consider the product \(\arccot x\;\tan x\):
+\[
+\begin{aligned}
+\frac{d}{dx}\bigl(\arccot x\;\tan x\bigr)
+&amp;= \arccot x\;\frac{d}{dx}\tan x
+      + \tan x\;\frac{d}{dx}\arccot x \\[4pt]
+&amp;= \arccot x\;\sec^{2}x
+      -\frac{\tan x}{1+x^{2}} .
+\end{aligned}
+\]
+Since \(\tan x = \dfrac{1}{\cot x}\),
+\[
+-\frac{\tan x}{1+x^{2}} = -\frac{1}{(x^{2}+1)\cot x},
+\]
+which is exactly the second term of \(y'\). Therefore  
+\[
+y' = \frac{d}{dx}\bigl(\arccot x\;\tan x\bigr).
+\]
+---
+### 4.  Integrate
+\[
+y = \arccot x\;\tan x + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+[FINAL ANSWER]
+\[
+\boxed{\,y = \arccot(x)\,\tan(x) + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \arccot(x)\,\tan(x) + C\,}</x:v>
+      </x:c>
+      <x:c r="J654" t="str">
+        <x:v>y^{\prime}=-\frac{\operatorname{acot}{(x)}(d)/(dx)\operatorname{ctan}{(x)}}{\operatorname{ctan}^{2}{(x)}}-\frac{1}{(x^{2}+1)\operatorname{ctan}{(x)}}</x:v>
+      </x:c>
+      <x:c r="K654" t="str">
+        <x:v>y ^ { prime } = - frac { operatorname { acot } { ( x ) } ( d ) / ( dx ) operatorname { ctan } { ( x ) } } { operatorname { ctan } ^ { 2 } { ( x ) } } - frac { 1 } { ( x ^ { 2 } + 1 ) operatorname { ctan } { ( x ) } }</x:v>
+      </x:c>
+      <x:c r="L654" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="M654" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N654" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="655">
-      <x:c r="A655"/>
-      <x:c r="B655"/>
+      <x:c r="A655" t="str">
+        <x:v>y^{\prime}=- \frac{\operatorname{acos}{\left(2 x \right)}}{\sqrt{1 - x^{2}} \operatorname{asin}^{2}{\left(x \right)}} - \frac{2}{\sqrt{1 - 4 x^{2}} \operatorname{asin}{\left(x \right)}}</x:v>
+      </x:c>
+      <x:c r="B655" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C655"/>
       <x:c r="D655"/>
-      <x:c r="E655"/>
-      <x:c r="F655"/>
-      <x:c r="G655"/>
+      <x:c r="E655" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F655" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G655" t="str">
+        <x:v>y=\arccos(2 \cdot x) \cdot \frac{1}{\arcsin(x)}+x^{2} \cdot \ln(x)+C</x:v>
+      </x:c>
       <x:c r="H655"/>
-      <x:c r="I655"/>
-      <x:c r="J655"/>
-      <x:c r="K655"/>
-      <x:c r="L655"/>
-      <x:c r="M655"/>
-      <x:c r="N655"/>
+      <x:c r="I655" t="str">
+        <x:v>[REASONING]
+**Solution**
+\[
+y'=- \frac{\arccos (2x)}{\sqrt{1-x^{2}}\;\bigl(\arcsin x\bigr)^{2}}
+      -\frac{2}{\sqrt{1-4x^{2}}\;\arcsin x},
+\qquad |x|&lt;\tfrac12 .
+\]
+---
+### 1.  Look for a function whose derivative gives the right‑hand side  
+Consider the quotient  
+\[
+u(x)=\frac{\arccos (2x)}{\arcsin x}.
+\]
+If \(y'=u'\), then \(y=u+C\).  
+Compute \(u'\) with the quotient rule.
+---
+### 2.  Derivatives of the numerator and denominator  
+\[
+\begin{aligned}
+A(x)&amp;=\arccos (2x), &amp;
+A'(x)&amp;=-\frac{2}{\sqrt{1-(2x)^{2}}}
+      =-\frac{2}{\sqrt{1-4x^{2}}},\\[4pt]
+B(x)&amp;=\arcsin x, &amp;
+B'(x)&amp;=\frac{1}{\sqrt{1-x^{2}}}.
+\end{aligned}
+\]
+---
+### 3.  Apply the quotient rule  
+\[
+u'=\frac{A'B-AB'}{B^{2}}.
+\]
+Insert the expressions found above:
+\[
+\begin{aligned}
+u'&amp;=\frac{\displaystyle
+\Bigl(-\frac{2}{\sqrt{1-4x^{2}}}\Bigr)\,\arcsin x
+      -\arccos (2x)\,\Bigl(\frac{1}{\sqrt{1-x^{2}}}\Bigr)}
+          {\bigl(\arcsin x\bigr)^{2}} \\[6pt]
+   &amp;= -\frac{2}{\sqrt{1-4x^{2}}\;\arcsin x}
+      -\frac{\arccos (2x)}{\sqrt{1-x^{2}}\;(\arcsin x)^{2}} .
+\end{aligned}
+\]
+The right‑hand side is exactly the given expression for \(y'\).
+Hence  
+\[
+y' = u' \quad\Longrightarrow\quad y = u + C.
+\]
+---
+### 4.  General solution  
+\[
+\boxed{\,y(x)=\frac{\arccos (2x)}{\arcsin x}+C\,},
+\qquad |x|&lt;\tfrac12 .
+\]
+The constant \(C\) is arbitrary, and the domain is the intersection of the domains of \(\arccos(2x)\) and \(\arcsin x\), i.e. \(|x|&lt;\tfrac12\).
+[FINAL ANSWER]
+\boxed{\,y(x)=\frac{\arccos (2x)}</x:v>
+      </x:c>
+      <x:c r="J655" t="str">
+        <x:v>y^{\prime}=-\frac{\operatorname{acos}{(2x)}}{\sqrt{1-x^{2}}\operatorname{asin}^{2}{(x)}}-\frac{2}{\sqrt{1-4x^{2}}\operatorname{asin}{(x)}}</x:v>
+      </x:c>
+      <x:c r="K655" t="str">
+        <x:v>y ^ { prime } = - frac { operatorname { acos } { ( 2 x ) } } { sqrt { 1 - x ^ { 2 } } operatorname { asin } ^ { 2 } { ( x ) } } - frac { 2 } { sqrt { 1 - 4 x ^ { 2 } } operatorname { asin } { ( x ) } }</x:v>
+      </x:c>
+      <x:c r="L655" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="M655" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N655" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="656">
-      <x:c r="A656"/>
-      <x:c r="B656"/>
+      <x:c r="A656" t="str">
+        <x:v>y^{\prime}=\frac{2 \sin{\left(2 x \right)} \operatorname{asin}{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{2}{\sqrt{1 - 4 x^{2}} \cos{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B656" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C656"/>
       <x:c r="D656"/>
-      <x:c r="E656"/>
-      <x:c r="F656"/>
-      <x:c r="G656"/>
+      <x:c r="E656" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F656" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G656" t="str">
+        <x:v>y=\arcsin(2 \cdot x) \cdot \frac{1}{\cos(2 \cdot x)}+\ctg(2 \cdot x) \cdot x^{2}+C</x:v>
+      </x:c>
       <x:c r="H656"/>
-      <x:c r="I656"/>
-      <x:c r="J656"/>
-      <x:c r="K656"/>
-      <x:c r="L656"/>
-      <x:c r="M656"/>
-      <x:c r="N656"/>
+      <x:c r="I656" t="str">
+        <x:v>[REASONING]
+[REASONING]
+The differential equation is  
+\[
+y'=\frac{2\sin(2x)\,\arcsin(2x)}{\cos^{2}(2x)}+\frac{2}{\sqrt{1-4x^{2}}\;\cos(2x)} .
+\]
+---
+### 1.  Recognize derivatives inside the terms  
+*Derivative of \(\sec(2x)\):*  
+\[
+\frac{d}{dx}\sec(2x)=2\sec(2x)\tan(2x)=\frac{2\sin(2x)}{\cos^{2}(2x)} .
+\]
+Hence  
+\[
+\frac{2\sin(2x)}{\cos^{2}(2x)} = \bigl(\sec(2x)\bigr)' .
+\]
+*Derivative of \(\arcsin(2x)\):*  
+\[
+\frac{d}{dx}\arcsin(2x)=\frac{2}{\sqrt{1-(2x)^{2}}}= \frac{2}{\sqrt{1-4x^{2}}}.
+\]
+Thus  
+\[
+\frac{2}{\sqrt{1-4x^{2}}}= \bigl(\arcsin(2x)\bigr)' .
+\]
+---
+### 2.  Rewrite the right‑hand side using these derivatives  
+\[
+\begin{aligned}
+y' &amp;=\arcsin(2x)\,\frac{2\sin(2x)}{\cos^{2}(2x)}+\frac{2}{\sqrt{1-4x^{2}}}\,\frac{1}{\cos(2x)}\\[4pt]
+   &amp;=\arcsin(2x)\,(\sec(2x))' + (\arcsin(2x))'\,\sec(2x).
+\end{aligned}
+\]
+---
+### 3.  Identify the product rule  
+The expression obtained is exactly the derivative of the product \(\arcsin(2x)\,\sec(2x)\):
+\[
+\frac{d}{dx}\bigl[\arcsin(2x)\,\sec(2x)\bigr]
+      =\arcsin(2x)\,(\sec(2x))' + (\arcsin(2x))'\,\sec(2x).
+\]
+Therefore  
+\[
+y' = \frac{d}{dx}\bigl[\arcsin(2x)\,\sec(2x)\bigr].
+\]
+---
+### 4.  Integrate  
+Integrating both sides with respect to \(x\),
+\[
+y = \arcsin(2x)\,\sec(2x) + C,
+\]
+where \(C\) is an arbitrary constant.
+---
+[FINAL ANSWER]  
+\[
+\boxed{\,y = \sec(2x)\,\arcsin(2x) + C\,}
+\]
+[FINAL ANSWER]
+\boxed{\,y = \sec(2x)\,\arcsin(2x) + C\,}</x:v>
+      </x:c>
+      <x:c r="J656" t="str">
+        <x:v>y^{\prime}=\frac{2\sin{(2x)}\operatorname{asin}{(2x)}}{\cos^{2}{(2x)}}+\frac{2}{\sqrt{1-4x^{2}}\cos{(2x)}}</x:v>
+      </x:c>
+      <x:c r="K656" t="str">
+        <x:v>y ^ { prime } = frac { 2 sin { ( 2 x ) } operatorname { asin } { ( 2 x ) } } { cos ^ { 2 } { ( 2 x ) } } + frac { 2 } { sqrt { 1 - 4 x ^ { 2 } } cos { ( 2 x ) } }</x:v>
+      </x:c>
+      <x:c r="L656" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M656" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N656" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="657">
-      <x:c r="A657"/>
-      <x:c r="B657"/>
+      <x:c r="A657" t="str">
+        <x:v>y^{\prime}=\frac{e^{x} \left(- 2 \tan^{2}{\left(2 x \right)} - 2\right)}{\tan^{2}{\left(2 x \right)}} + \frac{e^{x} \log{\left(e \right)}}{\tan{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B657" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C657"/>
       <x:c r="D657"/>
-      <x:c r="E657"/>
-      <x:c r="F657"/>
-      <x:c r="G657"/>
+      <x:c r="E657" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F657" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G657" t="str">
+        <x:v>y=e^{x} \cdot \frac{1}{\tg(2 \cdot x)}+\arcsin(x) \cdot \ln(x)+C</x:v>
+      </x:c>
       <x:c r="H657"/>
-      <x:c r="I657"/>
-      <x:c r="J657"/>
-      <x:c r="K657"/>
-      <x:c r="L657"/>
-      <x:c r="M657"/>
-      <x:c r="N657"/>
+      <x:c r="I657" t="str">
+        <x:v>[REASONING]
+**Step 1 – Simplify the right‑hand side**
+\[
+y'=\frac{e^{x}\bigl(-2\tan^{2}(2x)-2\bigr)}{\tan^{2}(2x)}+\frac{e^{x}\log(e)}{\tan(2x)}
+\]
+Since \(\log(e)=1\),
+\[
+y' = e^{x}\Bigl[\frac{-2(\tan^{2}(2x)+1)}{\tan^{2}(2x)}+\frac{1}{\tan(2x)}\Bigr].
+\]
+Use \(\tan^{2}\theta+1=\sec^{2}\theta\) and \(\displaystyle\frac{\sec^{2}\theta}{\tan^{2}\theta}= \csc^{2}\theta\):
+\[
+\frac{-2(\tan^{2}(2x)+1)}{\tan^{2}(2x)} = -2\csc^{2}(2x),\qquad
+\frac{1}{\tan(2x)} = \cot(2x).
+\]
+Hence  
+\[
+\boxed{y' = e^{x}\bigl[-2\csc^{2}(2x)+\cot(2x)\bigr]}.
+\]
+---
+**Step 2 – Look for a factor \(e^{x}\)**  
+Write \(y\) as \(y=e^{x}f(x)\). Then  
+\[
+y' = e^{x}f + e^{x}f' = e^{x}\bigl(f+f'\bigr).
+\]
+Comparing with the expression for \(y'\),
+\[
+f'+f = -2\csc^{2}(2x)+\cot(2x).\tag{1}
+\]
+---
+**Step 3 – Solve the linear ODE for \(f\)**  
+Observe that  
+\[
+\frac{d}{dx}\cot(2x) = -2\csc^{2}(2x).
+\]
+Thus  
+\[
+-2\csc^{2}(2x)+\cot(2x)=\frac{d}{dx}\cot(2x)+\cot(2x).
+\]
+Therefore a particular solution of (1) is  
+\[
+f_{p}(x)=\cot(2x),
+\]
+because \(f_{p}'+f_{p}= (\cot(2x))'+\cot(2x)= -2\csc^{2}(2x)+\cot(2x)\).
+The homogeneous equation \(f'+f=0\) gives  
+\[
+f_{h}(x)=C e^{-x},
+\]
+with constant \(C\).
+Hence  
+\[
+f(x)=\cot(2x)+C e^{-x}.
+\]
+---
+**Step 4 – Obtain \(y\)**  
+\[
+y = e^{x}f(x)=e^{x}\bigl[\cot(2x)+C e^{-x}\bigr]
+      = e^{x}\cot(2x)+C.
+\]
+---
+**Final solution**
+\[
+\boxed{\,y(x)=e^{x}\cot(2x)+C\,}
+\] 
+where \(C\) is an arbitrary constant.
+[FINAL ANSWER]
+\boxed{\,y(x)=e^{x}</x:v>
+      </x:c>
+      <x:c r="J657" t="str">
+        <x:v>y^{\prime}=\frac{exp(x)(-2\tan^{2}{(2x)}-2)}{\tan^{2}{(2x)}}+\frac{exp(x)\log{(e)}}{\tan{(2x)}}</x:v>
+      </x:c>
+      <x:c r="K657" t="str">
+        <x:v>y ^ { prime } = frac { exp ( x ) ( - 2 tan ^ { 2 } { ( 2 x ) } - 2 ) } { tan ^ { 2 } { ( 2 x ) } } + frac { exp ( x ) log { ( e ) } } { tan { ( 2 x ) } }</x:v>
+      </x:c>
+      <x:c r="L657" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="M657" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N657" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="658">
-      <x:c r="A658"/>
-      <x:c r="B658"/>
+      <x:c r="A658" t="str">
+        <x:v>y^{\prime}=\frac{2 \log{\left(x \right)} \sin{\left(2 x \right)}}{\cos^{2}{\left(2 x \right)}} + \frac{1}{x \cos{\left(2 x \right)}}</x:v>
+      </x:c>
+      <x:c r="B658" t="str">
+        <x:v>separable variables</x:v>
+      </x:c>
       <x:c r="C658"/>
       <x:c r="D658"/>
-      <x:c r="E658"/>
-      <x:c r="F658"/>
-      <x:c r="G658"/>
+      <x:c r="E658" t="str">
+        <x:v>separable</x:v>
+      </x:c>
+      <x:c r="F658" t="str">
+        <x:v>separable_train.xlsx</x:v>
+      </x:c>
+      <x:c r="G658" t="str">
+        <x:v>y=\ln(x) \cdot \frac{1}{\cos(2 \cdot x)}-\tg(2 \cdot x) \cdot \ln(x)+C</x:v>
+      </x:c>
       <x:c r="H658"/>
-      <x:c r="I658"/>
-      <x:c r="J658"/>
-      <x:c r="K658"/>
-      <x:c r="L658"/>
-      <x:c r="M658"/>
-      <x:c r="N658"/>
+      <x:c r="I658" t="str">
+        <x:v>[REASONING]
+**Step‑by‑step solution**
+\[
+y'=\frac{2\log x\,\sin (2x)}{\cos ^2(2x)}+\frac{1}{x\cos (2x)}
+\qquad (x&gt;0,\; \cos 2x\neq 0)
+\]
+---
+### 1.  Look for a function whose derivative gives the right‑hand side  
+Consider  
+\[
+u(x)=\frac{\log x}{\cos (2x)}=\log x\;\sec (2x).
+\]
+Using the product rule  
+\[
+u'(x)=\bigl(\log x\bigr)'\,\sec (2x)+\log x\;\bigl(\sec (2x)\bigr)' .
+\]
+Compute each derivative:
+* \((\log x)'=\dfrac{1}{x}\).
+* \(\displaystyle \bigl(\sec (2x)\bigr)'=
+\sec (2x)\tan (2x)\cdot (2)=2\sec (2x)\tan (2x).\)
+Recall \(\sec (2x)=\dfrac{1}{\cos (2x)}\) and \(\tan (2x)=\dfrac{\sin (2x)}{\cos (2x)}\); therefore  
+\[
+2\sec (2x)\tan (2x)=2\frac{1}{\cos (2x)}\frac{\sin (2x)}{\cos (2x)}
+= \frac{2\sin (2x)}{\cos ^2(2x)} .
+\]
+Now substitute back:
+\[
+\begin{aligned}
+u'(x) &amp;=
+\frac{1}{x}\,\frac{1}{\cos (2x)}
++\log x\;\frac{2\sin (2x)}{\cos ^2(2x)}  \\
+&amp;= \frac{1}{x\cos (2x)}+\frac{2\log x\,\sin (2x)}{\cos ^2(2x)} .
+\end{aligned}
+\]
+The expression obtained for \(u'(x)\) is exactly the right‑hand side of the given differential equation.
+Hence  
+\[
+y' = u'(x)=\frac{d}{dx}\!\left(\frac{\log x}{\cos (2x)}\right).
+\]
+---
+### 2.  Integrate  
+\[
+y = \int y'\,dx = \int u'(x)\,dx = u(x)+C
+      = \frac{\log x}{\cos (2x)}+C .
+\]
+---
+\[
+\boxed{\,y(x)=\dfrac{\ln x}{\cos (2x)}+C\,}
+\]
+where \(C\) is an arbitrary constant, and the solution is valid for \(x&gt;0\) with \(\cos(2x)\neq 0\).
+[FINAL ANSWER]
+\boxed{\,y(x)=\dfrac{\ln x}</x:v>
+      </x:c>
+      <x:c r="J658" t="str">
+        <x:v>y^{\prime}=\frac{2\log{(x)}\sin{(2x)}}{\cos^{2}{(2x)}}+\frac{1}{x\cos{(2x)}}</x:v>
+      </x:c>
+      <x:c r="K658" t="str">
+        <x:v>y ^ { prime } = frac { 2 log { ( x ) } sin { ( 2 x ) } } { cos ^ { 2 } { ( 2 x ) } } + frac { 1 } { x cos { ( 2 x ) } }</x:v>
+      </x:c>
+      <x:c r="L658" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M658" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N658" t="str">
+        <x:v>train</x:v>
+      </x:c>
     </x:row>
     <x:row r="659">
       <x:c r="A659"/>
